--- a/data/trans_orig/P36$cafe-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P36$cafe-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>647883</t>
+          <t>646570</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>670348</t>
+          <t>669481</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>637357</t>
+          <t>636060</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>659703</t>
+          <t>659573</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,47 +782,47 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
+          <t>95,82%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1304</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1308612</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>1292671</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>1323904</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>94,73%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>93,58%</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
           <t>95,84%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1304</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1308612</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>1290482</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>1324704</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>94,73%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>93,42%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>95,9%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10735</t>
+          <t>11044</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29699</t>
+          <t>29272</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27801</t>
+          <t>28282</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>51981</t>
+          <t>51327</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>43786</t>
+          <t>43968</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>72174</t>
+          <t>71623</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,18%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21662</t>
+          <t>20659</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>43771</t>
+          <t>43729</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4905</t>
+          <t>4859</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17527</t>
+          <t>17630</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>29192</t>
+          <t>29966</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>55067</t>
+          <t>54274</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6835</t>
+          <t>7608</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20405</t>
+          <t>22133</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4742</t>
+          <t>5363</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17541</t>
+          <t>18240</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15033</t>
+          <t>14736</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34779</t>
+          <t>32397</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>4691</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15624</t>
+          <t>15402</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10287</t>
+          <t>10220</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>26228</t>
+          <t>26274</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>17203</t>
+          <t>17103</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>36545</t>
+          <t>36785</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -1297,12 +1297,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>496491</t>
+          <t>499565</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>543189</t>
+          <t>543871</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1312,12 +1312,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>71,64%</t>
+          <t>72,08%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>78,38%</t>
+          <t>78,48%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>534682</t>
+          <t>532008</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>574156</t>
+          <t>574339</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>77,68%</t>
+          <t>77,29%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>83,41%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1367,12 +1367,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1043954</t>
+          <t>1044671</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1103589</t>
+          <t>1105621</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1382,12 +1382,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>75,57%</t>
+          <t>75,63%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>80,04%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>880462</t>
+          <t>880862</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>911005</t>
+          <t>911302</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>876817</t>
+          <t>874821</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>909974</t>
+          <t>910512</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1766987</t>
+          <t>1765875</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1813875</t>
+          <t>1811546</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,04%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>67353</t>
+          <t>66042</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>103612</t>
+          <t>103302</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>92410</t>
+          <t>92817</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>132428</t>
+          <t>135085</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>168061</t>
+          <t>169567</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>223944</t>
+          <t>225471</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,71%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>30870</t>
+          <t>30416</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>59138</t>
+          <t>58879</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>22491</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>47978</t>
+          <t>46889</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>58552</t>
+          <t>59039</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>95559</t>
+          <t>96331</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12276</t>
+          <t>11549</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30494</t>
+          <t>29615</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,82 +1768,82 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
+          <t>1,2%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,09%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>14931</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>8722</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>26317</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>2,72%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>34256</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>24598</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>48183</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>1,78%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>1,28%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,18%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>14931</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>8724</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>23864</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>2,47%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>34256</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>23259</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>47674</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>1,78%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>1,21%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8121</t>
+          <t>7758</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>23682</t>
+          <t>23146</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7705</t>
+          <t>7416</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21559</t>
+          <t>21353</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>18375</t>
+          <t>17969</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>39411</t>
+          <t>39690</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -1979,12 +1979,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>754407</t>
+          <t>751555</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>803858</t>
+          <t>803435</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1994,12 +1994,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>78,68%</t>
+          <t>78,38%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>83,83%</t>
+          <t>83,79%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2014,12 +2014,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>737347</t>
+          <t>734724</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>787958</t>
+          <t>787182</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2029,12 +2029,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>76,22%</t>
+          <t>75,95%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>81,45%</t>
+          <t>81,37%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2049,12 +2049,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1507176</t>
+          <t>1505639</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1577340</t>
+          <t>1577190</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>78,16%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>81,88%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>587091</t>
+          <t>588812</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>620300</t>
+          <t>620398</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>86,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>606141</t>
+          <t>605634</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>636122</t>
+          <t>635292</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>88,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1206095</t>
+          <t>1204899</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1248937</t>
+          <t>1250250</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,84%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>57568</t>
+          <t>56336</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>90825</t>
+          <t>89502</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>79923</t>
+          <t>81180</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>117206</t>
+          <t>116433</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>149100</t>
+          <t>147119</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>196562</t>
+          <t>199069</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,62%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>15643</t>
+          <t>15177</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>37111</t>
+          <t>35793</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5040</t>
+          <t>5162</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>17688</t>
+          <t>18069</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>24572</t>
+          <t>22950</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>49327</t>
+          <t>47600</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9404</t>
+          <t>9393</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25847</t>
+          <t>25790</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6007</t>
+          <t>6034</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19538</t>
+          <t>20296</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17860</t>
+          <t>18437</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>40577</t>
+          <t>38402</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10701</t>
+          <t>10864</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>27015</t>
+          <t>28259</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6825</t>
+          <t>7176</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>20742</t>
+          <t>20470</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>20553</t>
+          <t>20844</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>42912</t>
+          <t>41322</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -2661,12 +2661,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>478253</t>
+          <t>482404</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>526618</t>
+          <t>531156</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2676,12 +2676,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>71,21%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2696,12 +2696,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>494008</t>
+          <t>493602</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>536742</t>
+          <t>539497</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2711,12 +2711,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>72,18%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>78,49%</t>
+          <t>78,89%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2731,12 +2731,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>990302</t>
+          <t>988846</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1057920</t>
+          <t>1055041</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2746,12 +2746,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>72,75%</t>
+          <t>72,64%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>77,71%</t>
+          <t>77,5%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>810976</t>
+          <t>809871</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>848838</t>
+          <t>848311</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>903095</t>
+          <t>902624</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>943984</t>
+          <t>943479</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1726282</t>
+          <t>1723107</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1781334</t>
+          <t>1780663</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,11%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>75555</t>
+          <t>75721</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>109832</t>
+          <t>112462</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>91388</t>
+          <t>91093</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>133481</t>
+          <t>131671</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>178094</t>
+          <t>176867</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>231591</t>
+          <t>230318</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,66%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>13195</t>
+          <t>13209</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>29681</t>
+          <t>30810</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>10810</t>
+          <t>10007</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>27829</t>
+          <t>28294</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>27153</t>
+          <t>27058</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>50842</t>
+          <t>50365</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12754</t>
+          <t>12197</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>29036</t>
+          <t>29353</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10936</t>
+          <t>10529</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>27192</t>
+          <t>27985</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>27040</t>
+          <t>27456</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>49576</t>
+          <t>50778</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>11668</t>
+          <t>10986</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>30273</t>
+          <t>30694</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>7008</t>
+          <t>6372</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>21771</t>
+          <t>20683</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>21889</t>
+          <t>21553</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>44346</t>
+          <t>44806</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -3343,12 +3343,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>668660</t>
+          <t>662482</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>719003</t>
+          <t>716223</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3358,12 +3358,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>70,44%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>76,45%</t>
+          <t>76,16%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3378,12 +3378,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>774797</t>
+          <t>774536</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>826996</t>
+          <t>826900</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>74,82%</t>
+          <t>74,79%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>79,85%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3413,12 +3413,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1452350</t>
+          <t>1456610</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1528323</t>
+          <t>1530642</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>73,5%</t>
+          <t>73,71%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>77,34%</t>
+          <t>77,46%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2953472</t>
+          <t>2958997</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3020686</t>
+          <t>3023394</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3055452</t>
+          <t>3056925</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3122071</t>
+          <t>3121659</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>6033195</t>
+          <t>6039299</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6125749</t>
+          <t>6126045</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>232577</t>
+          <t>232687</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>300228</t>
+          <t>298110</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>321891</t>
+          <t>327110</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>392999</t>
+          <t>401198</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>573255</t>
+          <t>575757</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>671909</t>
+          <t>672395</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,12%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>96616</t>
+          <t>96059</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>143034</t>
+          <t>140992</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>55733</t>
+          <t>55299</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>89664</t>
+          <t>88606</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>161452</t>
+          <t>162356</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>216795</t>
+          <t>215852</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>52059</t>
+          <t>52434</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>85648</t>
+          <t>84976</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,47 +3814,47 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>53550</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>41150</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>72259</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
           <t>1,59%</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>2,62%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>53550</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>39420</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>69792</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>1,59%</t>
-        </is>
-      </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>101491</t>
+          <t>101631</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>145377</t>
+          <t>144151</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>46331</t>
+          <t>44323</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>77733</t>
+          <t>76151</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>42427</t>
+          <t>42586</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>71113</t>
+          <t>71838</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>93955</t>
+          <t>93219</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>138486</t>
+          <t>136291</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -4025,12 +4025,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2447433</t>
+          <t>2451542</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2549606</t>
+          <t>2544753</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4040,12 +4040,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>74,97%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>77,83%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4060,12 +4060,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>2586715</t>
+          <t>2589879</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>2685599</t>
+          <t>2683530</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4075,12 +4075,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>76,64%</t>
+          <t>76,73%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>79,57%</t>
+          <t>79,51%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4095,12 +4095,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>5069578</t>
+          <t>5064353</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>5206523</t>
+          <t>5203467</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4110,12 +4110,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>76,21%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>78,35%</t>
+          <t>78,31%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>643422</t>
+          <t>642050</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>670123</t>
+          <t>670109</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,7 +4389,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>648314</t>
+          <t>648958</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>672049</t>
+          <t>672556</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1298687</t>
+          <t>1302031</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1335481</t>
+          <t>1337534</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,7%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>44787</t>
+          <t>45441</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>74909</t>
+          <t>74824</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>58858</t>
+          <t>57577</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>91808</t>
+          <t>93404</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>110986</t>
+          <t>109323</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>153645</t>
+          <t>155581</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,13%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27989</t>
+          <t>27632</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>50668</t>
+          <t>51555</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7271</t>
+          <t>7315</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>24327</t>
+          <t>23410</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>39482</t>
+          <t>38945</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>68935</t>
+          <t>67195</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7379</t>
+          <t>7533</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23599</t>
+          <t>24903</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2139</t>
+          <t>3009</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11875</t>
+          <t>13571</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13210</t>
+          <t>12766</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33049</t>
+          <t>31523</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1855</t>
+          <t>1738</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11013</t>
+          <t>10030</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3475</t>
+          <t>3109</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14927</t>
+          <t>14114</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6725</t>
+          <t>6042</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>21327</t>
+          <t>19883</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -4939,12 +4939,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>555535</t>
+          <t>558486</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>598334</t>
+          <t>599806</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>79,62%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>558536</t>
+          <t>557996</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>596701</t>
+          <t>598424</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>80,24%</t>
+          <t>80,16%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1128605</t>
+          <t>1129471</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1184969</t>
+          <t>1184352</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>80,82%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>84,79%</t>
+          <t>84,74%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>923711</t>
+          <t>924489</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>959009</t>
+          <t>959328</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>953810</t>
+          <t>953497</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>985088</t>
+          <t>986034</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1888461</t>
+          <t>1888738</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1935867</t>
+          <t>1935478</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,5%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>83044</t>
+          <t>81729</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>121743</t>
+          <t>121592</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>86379</t>
+          <t>86327</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>128591</t>
+          <t>129502</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>180758</t>
+          <t>179777</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>235672</t>
+          <t>237995</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,62%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>27441</t>
+          <t>26685</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>52637</t>
+          <t>51417</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8057</t>
+          <t>8163</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>23480</t>
+          <t>23230</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>39775</t>
+          <t>38915</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>67565</t>
+          <t>68751</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14294</t>
+          <t>14116</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37997</t>
+          <t>36143</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8965</t>
+          <t>9434</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27291</t>
+          <t>26228</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>26087</t>
+          <t>26781</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>54377</t>
+          <t>54024</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2977</t>
+          <t>3013</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>14369</t>
+          <t>13431</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3115</t>
+          <t>3152</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>14435</t>
+          <t>14933</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8034</t>
+          <t>8164</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>22868</t>
+          <t>23611</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -5621,12 +5621,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>784324</t>
+          <t>784820</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>838746</t>
+          <t>838901</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5636,12 +5636,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>77,1%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>82,4%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>860401</t>
+          <t>861361</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>907654</t>
+          <t>908894</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>83,62%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1665790</t>
+          <t>1664847</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1736948</t>
+          <t>1734499</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>81,33%</t>
+          <t>81,29%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>84,69%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>645103</t>
+          <t>647486</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>683389</t>
+          <t>683094</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>85,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>693515</t>
+          <t>692630</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>724809</t>
+          <t>724627</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1351320</t>
+          <t>1352008</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1400574</t>
+          <t>1399959</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>88,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,39%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>96837</t>
+          <t>97683</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>142775</t>
+          <t>142387</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>95313</t>
+          <t>97452</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>138063</t>
+          <t>138769</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>202070</t>
+          <t>203724</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>263561</t>
+          <t>261635</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,08%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>27032</t>
+          <t>27081</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>52209</t>
+          <t>52720</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5984,7 +5984,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>15410</t>
+          <t>15354</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>37708</t>
+          <t>37499</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>48544</t>
+          <t>47189</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>80753</t>
+          <t>79475</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11518</t>
+          <t>11682</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30567</t>
+          <t>30795</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10543</t>
+          <t>10955</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>31188</t>
+          <t>29516</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>26041</t>
+          <t>26803</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>51147</t>
+          <t>51610</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2877</t>
+          <t>2905</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>18890</t>
+          <t>18359</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5493</t>
+          <t>5315</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>22095</t>
+          <t>21792</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>11245</t>
+          <t>10647</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>32388</t>
+          <t>33298</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -6303,12 +6303,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>571688</t>
+          <t>572144</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>619959</t>
+          <t>617872</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6318,12 +6318,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>75,72%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>81,77%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6338,12 +6338,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>604673</t>
+          <t>601698</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>649310</t>
+          <t>647430</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6353,12 +6353,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>77,9%</t>
+          <t>77,52%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>83,41%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6373,12 +6373,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1191767</t>
+          <t>1186028</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1259148</t>
+          <t>1252533</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6388,12 +6388,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>77,8%</t>
+          <t>77,43%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>81,77%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>843612</t>
+          <t>840943</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>879116</t>
+          <t>878274</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>88,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>966769</t>
+          <t>966467</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>997332</t>
+          <t>997580</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1819880</t>
+          <t>1819587</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1868781</t>
+          <t>1866881</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,55%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>113694</t>
+          <t>112762</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>154605</t>
+          <t>155543</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>126964</t>
+          <t>129253</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>175607</t>
+          <t>172921</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>255007</t>
+          <t>257821</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>319288</t>
+          <t>319182</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>15,99%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>19624</t>
+          <t>20729</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>41354</t>
+          <t>42760</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>20587</t>
+          <t>20203</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>44222</t>
+          <t>42525</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>45690</t>
+          <t>46070</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>78476</t>
+          <t>77007</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,86%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>21885</t>
+          <t>21716</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>47664</t>
+          <t>48183</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13008</t>
+          <t>12787</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>31664</t>
+          <t>31173</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>40002</t>
+          <t>39806</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>70677</t>
+          <t>71248</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>9218</t>
+          <t>9054</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>26993</t>
+          <t>26518</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>7838</t>
+          <t>7743</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>23118</t>
+          <t>22506</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>20234</t>
+          <t>20081</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>43013</t>
+          <t>43326</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -6985,12 +6985,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>724027</t>
+          <t>723371</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>775490</t>
+          <t>774080</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -7000,12 +7000,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>76,55%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>81,84%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -7020,12 +7020,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>827042</t>
+          <t>825138</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>879328</t>
+          <t>878299</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -7035,12 +7035,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>78,6%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -7055,12 +7055,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1563491</t>
+          <t>1568766</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1635142</t>
+          <t>1639273</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7070,12 +7070,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>78,35%</t>
+          <t>78,61%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>82,14%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3095519</t>
+          <t>3092777</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3160006</t>
+          <t>3162417</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3293620</t>
+          <t>3292393</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3348714</t>
+          <t>3353797</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>6407334</t>
+          <t>6407585</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6499895</t>
+          <t>6497022</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,17%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>372498</t>
+          <t>373824</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>451700</t>
+          <t>450597</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>411155</t>
+          <t>407260</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>490463</t>
+          <t>490212</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>797553</t>
+          <t>800775</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>915117</t>
+          <t>916990</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,15%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>119496</t>
+          <t>121903</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>167878</t>
+          <t>167997</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,7 +7343,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>64011</t>
+          <t>65849</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>102198</t>
+          <t>104174</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>199328</t>
+          <t>197247</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>258091</t>
+          <t>260043</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>68931</t>
+          <t>71506</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>110026</t>
+          <t>112203</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>46694</t>
+          <t>47040</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>78507</t>
+          <t>79044</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>125629</t>
+          <t>127785</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>183500</t>
+          <t>179095</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>25950</t>
+          <t>25315</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>51016</t>
+          <t>50568</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>29090</t>
+          <t>29161</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>56910</t>
+          <t>54949</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>59747</t>
+          <t>61139</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>95957</t>
+          <t>95274</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -7667,12 +7667,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2694410</t>
+          <t>2695955</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2788728</t>
+          <t>2793756</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -7682,12 +7682,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>78,76%</t>
+          <t>78,81%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>81,67%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>2897471</t>
+          <t>2898251</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>2987930</t>
+          <t>2988337</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -7717,12 +7717,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>81,59%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>84,13%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>5614404</t>
+          <t>5616549</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>5748032</t>
+          <t>5749723</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>80,55%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>82,46%</t>
         </is>
       </c>
     </row>
@@ -8016,12 +8016,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>581553</t>
+          <t>581110</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>613756</t>
+          <t>613935</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>627279</t>
+          <t>627297</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>649045</t>
+          <t>649933</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1216175</t>
+          <t>1215961</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1254672</t>
+          <t>1257350</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,51%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>69388</t>
+          <t>67219</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>102612</t>
+          <t>102217</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>67061</t>
+          <t>68134</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>102862</t>
+          <t>101979</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>145922</t>
+          <t>146898</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>195474</t>
+          <t>194401</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,46%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>55197</t>
+          <t>55546</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>86168</t>
+          <t>85897</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>40889</t>
+          <t>41590</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>70101</t>
+          <t>70603</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>102468</t>
+          <t>104039</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>144718</t>
+          <t>146661</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,91%</t>
         </is>
       </c>
     </row>
@@ -8355,12 +8355,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10763</t>
+          <t>10846</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29196</t>
+          <t>29534</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4373</t>
+          <t>4358</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15910</t>
+          <t>16373</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8410,7 +8410,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8425,12 +8425,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17338</t>
+          <t>17620</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>38524</t>
+          <t>40037</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>32478</t>
+          <t>32818</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>59161</t>
+          <t>57106</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>24504</t>
+          <t>24208</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>47803</t>
+          <t>47219</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>62044</t>
+          <t>62803</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>97542</t>
+          <t>97092</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,22%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>520882</t>
+          <t>521825</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>564515</t>
+          <t>566872</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>77,4%</t>
+          <t>77,54%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>84,23%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>552318</t>
+          <t>552784</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>589061</t>
+          <t>590758</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>82,23%</t>
+          <t>82,3%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1087666</t>
+          <t>1088352</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1142592</t>
+          <t>1145572</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>85,19%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>888914</t>
+          <t>890220</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>930405</t>
+          <t>931662</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>934161</t>
+          <t>935668</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>969336</t>
+          <t>970857</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1837416</t>
+          <t>1836373</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1893235</t>
+          <t>1891306</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,66%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>113991</t>
+          <t>115049</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>161631</t>
+          <t>161237</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>121558</t>
+          <t>121043</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>166886</t>
+          <t>169323</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>249408</t>
+          <t>251917</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>319058</t>
+          <t>314467</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,24%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>86822</t>
+          <t>85749</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>126723</t>
+          <t>126700</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,7 +8939,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>74479</t>
+          <t>73573</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>111321</t>
+          <t>111935</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>174774</t>
+          <t>173609</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>228880</t>
+          <t>226271</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>10,97%</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11469</t>
+          <t>10479</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31187</t>
+          <t>30022</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9052,12 +9052,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6631</t>
+          <t>6517</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20718</t>
+          <t>20974</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9087,12 +9087,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21415</t>
+          <t>21522</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>45754</t>
+          <t>44355</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9127,7 +9127,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>28314</t>
+          <t>29972</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>55298</t>
+          <t>55093</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>34928</t>
+          <t>36398</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>64902</t>
+          <t>64630</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>71908</t>
+          <t>72767</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>108310</t>
+          <t>112605</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>843841</t>
+          <t>842239</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>890154</t>
+          <t>890473</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>87,19%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>870463</t>
+          <t>870681</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>914268</t>
+          <t>915647</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1727212</t>
+          <t>1722212</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1791564</t>
+          <t>1794667</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>83,71%</t>
+          <t>83,47%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>86,98%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>680877</t>
+          <t>679732</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>712257</t>
+          <t>710925</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9395,12 +9395,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>726056</t>
+          <t>726230</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>751210</t>
+          <t>752358</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1418973</t>
+          <t>1413012</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1456523</t>
+          <t>1454380</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,23%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>71247</t>
+          <t>75252</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>111777</t>
+          <t>113985</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>96348</t>
+          <t>95713</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>136807</t>
+          <t>135413</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>182551</t>
+          <t>182378</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>235301</t>
+          <t>237595</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,39%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>13886</t>
+          <t>14632</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>33959</t>
+          <t>33703</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>9095</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>24295</t>
+          <t>24945</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>26164</t>
+          <t>26315</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>50446</t>
+          <t>49700</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9696,7 +9696,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -9719,12 +9719,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6099</t>
+          <t>6011</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21402</t>
+          <t>21865</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9734,12 +9734,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2945</t>
+          <t>2933</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13078</t>
+          <t>13339</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11267</t>
+          <t>11744</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>29791</t>
+          <t>29811</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9804,7 +9804,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>12505</t>
+          <t>12965</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>32594</t>
+          <t>32713</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>15020</t>
+          <t>14687</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>34994</t>
+          <t>35122</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>32471</t>
+          <t>33212</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>60646</t>
+          <t>60709</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9917,7 +9917,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>628597</t>
+          <t>627829</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>667080</t>
+          <t>667551</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>82,78%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>685187</t>
+          <t>684152</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>719303</t>
+          <t>720367</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1327227</t>
+          <t>1326354</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1380555</t>
+          <t>1380686</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>85,93%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,45%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>854895</t>
+          <t>853404</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>886518</t>
+          <t>885480</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>965057</t>
+          <t>964231</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>995770</t>
+          <t>995257</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1828401</t>
+          <t>1828350</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1875153</t>
+          <t>1873527</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10152,7 +10152,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,61%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>105407</t>
+          <t>105469</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>147609</t>
+          <t>148921</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>109145</t>
+          <t>107520</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>156504</t>
+          <t>153038</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>226136</t>
+          <t>225027</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>285557</t>
+          <t>287758</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,53%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>40826</t>
+          <t>41771</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>69459</t>
+          <t>70990</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>39547</t>
+          <t>40210</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>70244</t>
+          <t>70846</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>86875</t>
+          <t>86936</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>127821</t>
+          <t>128640</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10378,7 +10378,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,5%</t>
         </is>
       </c>
     </row>
@@ -10401,12 +10401,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8438</t>
+          <t>8538</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>23833</t>
+          <t>24364</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3033</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>15399</t>
+          <t>14435</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>14345</t>
+          <t>14451</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>32847</t>
+          <t>33760</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -10514,12 +10514,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>20704</t>
+          <t>20979</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>42744</t>
+          <t>43266</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10529,82 +10529,82 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
+          <t>4,61%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>40112</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>28530</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>53464</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>3,85%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>2,74%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>5,13%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>70893</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>55913</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>90312</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>3,58%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>2,82%</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
           <t>4,56%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>40112</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>29527</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>55194</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>3,85%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>2,83%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>5,29%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>70893</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>55574</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>89849</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>3,58%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>2,81%</t>
-        </is>
-      </c>
-      <c r="W26" s="2" t="inlineStr">
-        <is>
-          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -10627,12 +10627,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>778443</t>
+          <t>777203</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>822861</t>
+          <t>821939</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -10642,12 +10642,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -10662,12 +10662,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>911101</t>
+          <t>912547</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>953240</t>
+          <t>952365</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10677,12 +10677,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>87,52%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -10697,12 +10697,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1708116</t>
+          <t>1705491</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1764598</t>
+          <t>1764833</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -10712,12 +10712,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>86,13%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>89,12%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3042692</t>
+          <t>3042248</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3113510</t>
+          <t>3110167</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3284043</t>
+          <t>3280832</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3342862</t>
+          <t>3341743</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>6350672</t>
+          <t>6352029</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6437806</t>
+          <t>6437817</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,7 +10829,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>402872</t>
+          <t>405948</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>485161</t>
+          <t>481800</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>431133</t>
+          <t>432130</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>512593</t>
+          <t>512662</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>855408</t>
+          <t>857136</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>969735</t>
+          <t>970154</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,0%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>223018</t>
+          <t>224167</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>285211</t>
+          <t>283870</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>190784</t>
+          <t>184554</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>249273</t>
+          <t>243990</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>422754</t>
+          <t>427114</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>507743</t>
+          <t>512394</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,39%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>49710</t>
+          <t>49934</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>84215</t>
+          <t>82559</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11103,7 +11103,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>25221</t>
+          <t>24758</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>49154</t>
+          <t>48971</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>81086</t>
+          <t>81435</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>119229</t>
+          <t>120669</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11173,7 +11173,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>113648</t>
+          <t>114546</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>162985</t>
+          <t>164189</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>124407</t>
+          <t>126126</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>171662</t>
+          <t>175735</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>251000</t>
+          <t>248685</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>318902</t>
+          <t>320337</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -11309,12 +11309,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2818906</t>
+          <t>2821863</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2905461</t>
+          <t>2902886</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -11324,12 +11324,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -11344,12 +11344,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>3063207</t>
+          <t>3060392</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>3145274</t>
+          <t>3139268</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -11359,12 +11359,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>86,42%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -11379,12 +11379,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>5906603</t>
+          <t>5909064</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>6025465</t>
+          <t>6020041</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -11394,12 +11394,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>85,25%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>86,85%</t>
         </is>
       </c>
     </row>
